--- a/data/sources/countries/nicaragua.xlsx
+++ b/data/sources/countries/nicaragua.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +48,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,377 +414,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI130"/>
+  <dimension ref="A1:BE130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="80" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id_Investment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Id_Investment_Original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Id_Seq</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_ALPHA3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_NUM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Province_ISO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Area_EN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Area_ES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Detail_ES</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Detail_EN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Joint_Venture</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Origin_Of_Seller</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Project_Type</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>News</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Caso1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Link1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Caso2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Link2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Caso3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Link3</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Caso4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link4</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Caso5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Caso6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Link6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Caso7</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Link7</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Caso8</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Link8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Caso9</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Link9</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Caso10</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Link10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Caso11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Link11</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Caso12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Link12</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Caso13</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Link13</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Caso14</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Link14</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>reliability_score</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>reliability_notes</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled_motivo</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source3</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>source4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>source5</t>
         </is>
       </c>
     </row>
@@ -824,7 +728,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -839,7 +743,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>Comunications Construction Company Limited</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -891,10 +795,10 @@
       <c r="BA2" t="n">
         <v>4</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BB2" t="n">
         <v>0</v>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>https://www.prensa-latina.cu/2025/12/24/funciona-en-nicaragua-mayor-planta-siderurgica-de-centroamerica/</t>
         </is>
@@ -924,7 +828,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -939,7 +843,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>Comunications Construction Company Limited</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -991,7 +895,7 @@
       <c r="BA3" t="n">
         <v>4</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BB3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1019,7 +923,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -1034,7 +938,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Zhong Fu Development</t>
+          <t>American Recycling</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1086,13 +990,8 @@
       <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="BC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
+      <c r="BB4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1119,7 +1018,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -1134,7 +1033,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company Ltd. (CCCC)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1191,20 +1090,20 @@
       <c r="BA5" t="n">
         <v>5</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BB5" t="n">
         <v>0</v>
       </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>https://www.pv-magazine.com/2025/06/13/nicaragua-starts-work-on-70-mw-solar-plant-largest-to-date/</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>https://www.telesurenglish.net/nicaragua-and-china-break-ground-on-landmark-solar-project-to-power-water-access-and-energy-sovereignty/</t>
+        </is>
+      </c>
       <c r="BE5" t="inlineStr">
-        <is>
-          <t>https://www.pv-magazine.com/2025/06/13/nicaragua-starts-work-on-70-mw-solar-plant-largest-to-date/</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>https://www.telesurenglish.net/nicaragua-and-china-break-ground-on-landmark-solar-project-to-power-water-access-and-energy-sovereignty/</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
         <is>
           <t>https://fundacionandresbello.org/en/news/nicaragua-%F0%9F%87%B3%F0%9F%87%AE-news/chinese-company-begins-construction-of-a-solar-plant-in-nicaragua/</t>
         </is>
@@ -1234,7 +1133,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -1249,7 +1148,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company Ltd. (CCCC)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1306,20 +1205,20 @@
       <c r="BA6" t="n">
         <v>5</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BB6" t="n">
         <v>0</v>
       </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>https://www.pv-magazine-latam.com/2025/03/25/anuncian-en-nicaragua-el-inicio-de-construccion-de-la-planta-fotovoltaica-el-hato-de-6735-mw/</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>https://newenergyevents.com/nicaragua-and-china-begin-construction-of-us80-million-el-hato-solar-plant/</t>
+        </is>
+      </c>
       <c r="BE6" t="inlineStr">
-        <is>
-          <t>https://www.pv-magazine-latam.com/2025/03/25/anuncian-en-nicaragua-el-inicio-de-construccion-de-la-planta-fotovoltaica-el-hato-de-6735-mw/</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>https://newenergyevents.com/nicaragua-and-china-begin-construction-of-us80-million-el-hato-solar-plant/</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/162502-con-la-tecnologia-solar-mas-avanzada-de-china-nicaragua-inicia-obras-de-la-planta-fotovoltaica-el-hato</t>
         </is>
@@ -1349,7 +1248,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -1364,7 +1263,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Zhong Fu Development</t>
+          <t>Zhong Fu Development S.A.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1418,25 +1317,20 @@
       <c r="BA7" t="n">
         <v>5</v>
       </c>
-      <c r="BC7" t="n">
-        <v>1</v>
+      <c r="BB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>https://confidencial.digital/en/english/chinese-mining-firms-now-control-more-than-one-million-hectares-in-nicaragua/</t>
+        </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.infobae.com/nicaragua/2026/03/20/el-regimen-de-nicaragua-autoriza-nueva-concesion-minera-a-empresa-china/</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
-        <is>
-          <t>https://confidencial.digital/en/english/chinese-mining-firms-now-control-more-than-one-million-hectares-in-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>https://www.infobae.com/nicaragua/2026/03/20/el-regimen-de-nicaragua-autoriza-nueva-concesion-minera-a-empresa-china/</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
         <is>
           <t>https://www.articulo66.com/2026/03/19/nueva-empresa-minera-china-concesion-nicaragua/</t>
         </is>
@@ -1466,7 +1360,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -1481,7 +1375,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>CIDCA</t>
+          <t>Agencia China de Cooperacion Internacional para el Desarrollo (CIDCA)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1538,20 +1432,20 @@
       <c r="BA8" t="n">
         <v>5</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BB8" t="n">
         <v>0</v>
       </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>https://www.el19digital.com/articulos/ver/139024-nicaragua-y-china-inician-fase-i-del-programa-nacional-de-viviendas-nuevas-victorias</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>https://www.prensa-latina.cu/2025/02/11/avanza-en-nicaragua-proyecto-de-viviendas-con-apoyo-de-china/</t>
+        </is>
+      </c>
       <c r="BE8" t="inlineStr">
-        <is>
-          <t>https://www.el19digital.com/articulos/ver/139024-nicaragua-y-china-inician-fase-i-del-programa-nacional-de-viviendas-nuevas-victorias</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>https://www.prensa-latina.cu/2025/02/11/avanza-en-nicaragua-proyecto-de-viviendas-con-apoyo-de-china/</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
         <is>
           <t>https://www.laprensani.com/2023/10/30/economia/3227961-se-le-cae-a-ortega-otra-mentira-sobre-la-regalia-de-mas-de-12000-viviendas-por-parte-de-china</t>
         </is>
@@ -1581,7 +1475,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -1596,7 +1490,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1653,25 +1547,20 @@
       <c r="BA9" t="n">
         <v>5</v>
       </c>
-      <c r="BC9" t="n">
-        <v>1</v>
+      <c r="BB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -1701,7 +1590,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -1716,7 +1605,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1773,25 +1662,20 @@
       <c r="BA10" t="n">
         <v>5</v>
       </c>
-      <c r="BC10" t="n">
-        <v>1</v>
+      <c r="BB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -1821,7 +1705,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -1836,7 +1720,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1893,25 +1777,20 @@
       <c r="BA11" t="n">
         <v>5</v>
       </c>
-      <c r="BC11" t="n">
-        <v>1</v>
+      <c r="BB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -1941,7 +1820,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -1956,7 +1835,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2013,25 +1892,20 @@
       <c r="BA12" t="n">
         <v>5</v>
       </c>
-      <c r="BC12" t="n">
-        <v>1</v>
+      <c r="BB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -2061,7 +1935,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -2076,7 +1950,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2133,25 +2007,20 @@
       <c r="BA13" t="n">
         <v>5</v>
       </c>
-      <c r="BC13" t="n">
-        <v>1</v>
+      <c r="BB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -2181,7 +2050,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -2196,7 +2065,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2253,25 +2122,20 @@
       <c r="BA14" t="n">
         <v>5</v>
       </c>
-      <c r="BC14" t="n">
-        <v>1</v>
+      <c r="BB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -2301,7 +2165,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -2316,7 +2180,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2373,25 +2237,20 @@
       <c r="BA15" t="n">
         <v>5</v>
       </c>
-      <c r="BC15" t="n">
-        <v>1</v>
+      <c r="BB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -2421,7 +2280,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -2436,7 +2295,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2493,25 +2352,20 @@
       <c r="BA16" t="n">
         <v>5</v>
       </c>
-      <c r="BC16" t="n">
-        <v>1</v>
+      <c r="BB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -2541,7 +2395,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -2556,7 +2410,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2613,25 +2467,20 @@
       <c r="BA17" t="n">
         <v>5</v>
       </c>
-      <c r="BC17" t="n">
-        <v>1</v>
+      <c r="BB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -2661,7 +2510,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -2676,7 +2525,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2733,25 +2582,20 @@
       <c r="BA18" t="n">
         <v>5</v>
       </c>
-      <c r="BC18" t="n">
-        <v>1</v>
+      <c r="BB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -2781,7 +2625,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -2796,7 +2640,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2853,25 +2697,20 @@
       <c r="BA19" t="n">
         <v>5</v>
       </c>
-      <c r="BC19" t="n">
-        <v>1</v>
+      <c r="BB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -2901,7 +2740,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -2916,7 +2755,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2973,25 +2812,20 @@
       <c r="BA20" t="n">
         <v>5</v>
       </c>
-      <c r="BC20" t="n">
-        <v>1</v>
+      <c r="BB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -3021,7 +2855,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -3036,7 +2870,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3093,25 +2927,20 @@
       <c r="BA21" t="n">
         <v>5</v>
       </c>
-      <c r="BC21" t="n">
-        <v>1</v>
+      <c r="BB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -3141,7 +2970,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -3156,7 +2985,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>HKND Group</t>
+          <t>HKND Group (Wang Jing)</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3213,25 +3042,20 @@
       <c r="BA22" t="n">
         <v>5</v>
       </c>
-      <c r="BC22" t="n">
-        <v>1</v>
+      <c r="BB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
+        </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
-        <is>
-          <t>https://www.swissinfo.ch/spa/nicaragua-quita-a-wang-jing-la-concesi%C3%B3n-para-construir-el-gran-canal-interoc%C3%A9anico/77174907</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>https://www.laprensani.com/2024/05/08/politica/3316568-ortega-manda-a-reformar-la-lxey-del-canal-interoceanico-y-le-quita-la-concesion-a-wang-jing</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
         <is>
           <t>https://www.infobae.com/america/america-latina/2024/05/11/la-caida-del-fastuoso-proyecto-de-un-canal-interoceanico-en-nicaragua-que-construiria-un-oscuro-inversionista-chino/</t>
         </is>
@@ -3261,7 +3085,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -3276,7 +3100,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>CAMC Engineering</t>
+          <t>China CAMC Engineering Co., Ltd.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3333,15 +3157,15 @@
       <c r="BA23" t="n">
         <v>3</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BB23" t="n">
         <v>0</v>
       </c>
-      <c r="BE23" t="inlineStr">
+      <c r="BC23" t="inlineStr">
         <is>
           <t>https://www.bnamericas.com/en/news/nicaragua-and-china-sign-agreement-on-bluefields-deepwater-port</t>
         </is>
       </c>
-      <c r="BF23" t="inlineStr">
+      <c r="BD23" t="inlineStr">
         <is>
           <t>https://www.expedienteabierto.org/chinas-advance-in-nicaragua-an-update/</t>
         </is>
@@ -3371,7 +3195,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -3386,7 +3210,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company (CCCC)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3440,20 +3264,15 @@
       <c r="BA24" t="n">
         <v>2</v>
       </c>
-      <c r="BC24" t="n">
-        <v>1</v>
+      <c r="BB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>https://dialogue.earth/en/energy/renewables-rights-and-relations-chinese-solar-projects-in-nicaragua/</t>
+        </is>
       </c>
       <c r="BD24" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE24" t="inlineStr">
-        <is>
-          <t>https://dialogue.earth/en/energy/renewables-rights-and-relations-chinese-solar-projects-in-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BF24" t="inlineStr">
         <is>
           <t>https://www.pv-magazine.com/2025/06/13/nicaragua-starts-work-on-70-mw-solar-plant-largest-to-date/</t>
         </is>
@@ -3483,7 +3302,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -3498,7 +3317,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3552,25 +3371,20 @@
       <c r="BA25" t="n">
         <v>3</v>
       </c>
-      <c r="BC25" t="n">
-        <v>1</v>
+      <c r="BB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF25" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -3600,7 +3414,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -3615,7 +3429,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3669,25 +3483,20 @@
       <c r="BA26" t="n">
         <v>3</v>
       </c>
-      <c r="BC26" t="n">
-        <v>1</v>
+      <c r="BB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF26" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG26" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -3717,7 +3526,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -3732,7 +3541,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3786,25 +3595,20 @@
       <c r="BA27" t="n">
         <v>3</v>
       </c>
-      <c r="BC27" t="n">
-        <v>1</v>
+      <c r="BB27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF27" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG27" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -3834,7 +3638,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -3849,7 +3653,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3903,25 +3707,20 @@
       <c r="BA28" t="n">
         <v>3</v>
       </c>
-      <c r="BC28" t="n">
-        <v>1</v>
+      <c r="BB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF28" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG28" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -3951,7 +3750,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -3966,7 +3765,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4020,25 +3819,20 @@
       <c r="BA29" t="n">
         <v>3</v>
       </c>
-      <c r="BC29" t="n">
-        <v>1</v>
+      <c r="BB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF29" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -4068,7 +3862,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -4083,7 +3877,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4137,25 +3931,20 @@
       <c r="BA30" t="n">
         <v>3</v>
       </c>
-      <c r="BC30" t="n">
-        <v>1</v>
+      <c r="BB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF30" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -4185,7 +3974,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -4200,7 +3989,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4254,25 +4043,20 @@
       <c r="BA31" t="n">
         <v>3</v>
       </c>
-      <c r="BC31" t="n">
-        <v>1</v>
+      <c r="BB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF31" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -4302,7 +4086,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -4317,7 +4101,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4371,25 +4155,20 @@
       <c r="BA32" t="n">
         <v>3</v>
       </c>
-      <c r="BC32" t="n">
-        <v>1</v>
+      <c r="BB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -4419,7 +4198,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -4434,7 +4213,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4488,25 +4267,20 @@
       <c r="BA33" t="n">
         <v>3</v>
       </c>
-      <c r="BC33" t="n">
-        <v>1</v>
+      <c r="BB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF33" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -4536,7 +4310,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -4551,7 +4325,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4605,25 +4379,20 @@
       <c r="BA34" t="n">
         <v>3</v>
       </c>
-      <c r="BC34" t="n">
-        <v>1</v>
+      <c r="BB34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -4653,7 +4422,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -4668,7 +4437,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4722,25 +4491,20 @@
       <c r="BA35" t="n">
         <v>3</v>
       </c>
-      <c r="BC35" t="n">
-        <v>1</v>
+      <c r="BB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF35" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -4770,7 +4534,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -4785,7 +4549,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4839,25 +4603,20 @@
       <c r="BA36" t="n">
         <v>3</v>
       </c>
-      <c r="BC36" t="n">
-        <v>1</v>
+      <c r="BB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF36" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG36" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -4887,7 +4646,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -4902,7 +4661,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4956,25 +4715,20 @@
       <c r="BA37" t="n">
         <v>3</v>
       </c>
-      <c r="BC37" t="n">
-        <v>1</v>
+      <c r="BB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF37" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG37" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -5004,7 +4758,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -5019,7 +4773,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5073,25 +4827,20 @@
       <c r="BA38" t="n">
         <v>3</v>
       </c>
-      <c r="BC38" t="n">
-        <v>1</v>
+      <c r="BB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE38" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF38" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG38" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -5121,7 +4870,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -5136,7 +4885,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5190,25 +4939,20 @@
       <c r="BA39" t="n">
         <v>3</v>
       </c>
-      <c r="BC39" t="n">
-        <v>1</v>
+      <c r="BB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE39" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF39" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG39" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -5238,7 +4982,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -5253,7 +4997,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5307,25 +5051,20 @@
       <c r="BA40" t="n">
         <v>3</v>
       </c>
-      <c r="BC40" t="n">
-        <v>1</v>
+      <c r="BB40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD40" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE40" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF40" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG40" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -5355,7 +5094,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -5370,7 +5109,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5424,25 +5163,20 @@
       <c r="BA41" t="n">
         <v>3</v>
       </c>
-      <c r="BC41" t="n">
-        <v>1</v>
+      <c r="BB41" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE41" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF41" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG41" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -5472,7 +5206,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -5487,7 +5221,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5541,25 +5275,20 @@
       <c r="BA42" t="n">
         <v>3</v>
       </c>
-      <c r="BC42" t="n">
-        <v>1</v>
+      <c r="BB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF42" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG42" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -5589,7 +5318,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -5604,7 +5333,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5658,25 +5387,20 @@
       <c r="BA43" t="n">
         <v>3</v>
       </c>
-      <c r="BC43" t="n">
-        <v>1</v>
+      <c r="BB43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF43" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG43" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -5706,7 +5430,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -5721,7 +5445,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5775,25 +5499,20 @@
       <c r="BA44" t="n">
         <v>3</v>
       </c>
-      <c r="BC44" t="n">
-        <v>1</v>
+      <c r="BB44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF44" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG44" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -5823,7 +5542,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -5838,7 +5557,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5892,25 +5611,20 @@
       <c r="BA45" t="n">
         <v>3</v>
       </c>
-      <c r="BC45" t="n">
-        <v>1</v>
+      <c r="BB45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF45" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG45" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -5940,7 +5654,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -5955,7 +5669,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6009,25 +5723,20 @@
       <c r="BA46" t="n">
         <v>3</v>
       </c>
-      <c r="BC46" t="n">
-        <v>1</v>
+      <c r="BB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF46" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG46" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -6057,7 +5766,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -6072,7 +5781,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6126,25 +5835,20 @@
       <c r="BA47" t="n">
         <v>3</v>
       </c>
-      <c r="BC47" t="n">
-        <v>1</v>
+      <c r="BB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE47" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF47" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG47" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -6174,7 +5878,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -6189,7 +5893,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6243,25 +5947,20 @@
       <c r="BA48" t="n">
         <v>3</v>
       </c>
-      <c r="BC48" t="n">
-        <v>1</v>
+      <c r="BB48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE48" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF48" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG48" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -6291,7 +5990,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -6306,7 +6005,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6360,25 +6059,20 @@
       <c r="BA49" t="n">
         <v>3</v>
       </c>
-      <c r="BC49" t="n">
-        <v>1</v>
+      <c r="BB49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF49" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG49" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -6408,7 +6102,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -6423,7 +6117,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>China Civil Engineering Construction Corporation</t>
+          <t>China Civil Engineering Construction Corporation (CCECC)</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6477,25 +6171,20 @@
       <c r="BA50" t="n">
         <v>3</v>
       </c>
-      <c r="BC50" t="n">
-        <v>1</v>
+      <c r="BB50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
+        </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>cancelado</t>
+          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
-        <is>
-          <t>https://www.tercerainformacion.es/articulo/internacional/24/10/2023/china-y-nicaragua-suscriben-acuerdos-para-devolver-el-ferrocarril-al-pais-centroamericano/</t>
-        </is>
-      </c>
-      <c r="BF50" t="inlineStr">
-        <is>
-          <t>https://www.tn8.tv/nacionales/exclusiva-asi-avanza-el-proyecto-del-ferrocarril-que-construira-china-en-nicaragua/</t>
-        </is>
-      </c>
-      <c r="BG50" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/dos-ferrocarriles-construira-nicaragua-en-alianza-con-china/</t>
         </is>
@@ -6525,7 +6214,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -6540,7 +6229,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>China Huadian</t>
+          <t>Huadian Overseas Investment</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -6594,20 +6283,15 @@
       <c r="BA51" t="n">
         <v>3</v>
       </c>
-      <c r="BC51" t="n">
-        <v>1</v>
+      <c r="BB51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>https://jpmas.com.ni/mega-hydroelectric-project-will-be-developed-in-nicaragua-in-cooperation-with-china/</t>
+        </is>
       </c>
       <c r="BD51" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE51" t="inlineStr">
-        <is>
-          <t>https://jpmas.com.ni/mega-hydroelectric-project-will-be-developed-in-nicaragua-in-cooperation-with-china/</t>
-        </is>
-      </c>
-      <c r="BF51" t="inlineStr">
         <is>
           <t>https://jpmas.com.ni/estos-son-los-megaproyectos-que-desarrollara-nicaragua-en-cooperacion-con-china/</t>
         </is>
@@ -6637,7 +6321,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -6652,7 +6336,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6706,15 +6390,10 @@
       <c r="BA52" t="n">
         <v>2</v>
       </c>
-      <c r="BC52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD52" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE52" t="inlineStr">
+      <c r="BB52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC52" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -6744,7 +6423,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -6759,7 +6438,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -6813,15 +6492,10 @@
       <c r="BA53" t="n">
         <v>2</v>
       </c>
-      <c r="BC53" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD53" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE53" t="inlineStr">
+      <c r="BB53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC53" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -6851,7 +6525,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -6866,7 +6540,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -6920,15 +6594,10 @@
       <c r="BA54" t="n">
         <v>2</v>
       </c>
-      <c r="BC54" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD54" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE54" t="inlineStr">
+      <c r="BB54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC54" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -6958,7 +6627,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -6973,7 +6642,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7027,15 +6696,10 @@
       <c r="BA55" t="n">
         <v>2</v>
       </c>
-      <c r="BC55" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD55" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE55" t="inlineStr">
+      <c r="BB55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC55" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -7065,7 +6729,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -7080,7 +6744,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -7134,15 +6798,10 @@
       <c r="BA56" t="n">
         <v>2</v>
       </c>
-      <c r="BC56" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD56" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE56" t="inlineStr">
+      <c r="BB56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC56" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -7172,7 +6831,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -7187,7 +6846,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7241,15 +6900,10 @@
       <c r="BA57" t="n">
         <v>2</v>
       </c>
-      <c r="BC57" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD57" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE57" t="inlineStr">
+      <c r="BB57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC57" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -7279,7 +6933,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -7294,7 +6948,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7348,15 +7002,10 @@
       <c r="BA58" t="n">
         <v>2</v>
       </c>
-      <c r="BC58" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD58" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE58" t="inlineStr">
+      <c r="BB58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC58" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -7386,7 +7035,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -7401,7 +7050,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7455,15 +7104,10 @@
       <c r="BA59" t="n">
         <v>2</v>
       </c>
-      <c r="BC59" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD59" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE59" t="inlineStr">
+      <c r="BB59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC59" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -7493,7 +7137,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -7508,7 +7152,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7562,15 +7206,10 @@
       <c r="BA60" t="n">
         <v>2</v>
       </c>
-      <c r="BC60" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD60" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE60" t="inlineStr">
+      <c r="BB60" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC60" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -7600,7 +7239,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -7615,7 +7254,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -7669,15 +7308,10 @@
       <c r="BA61" t="n">
         <v>2</v>
       </c>
-      <c r="BC61" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD61" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE61" t="inlineStr">
+      <c r="BB61" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC61" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -7707,7 +7341,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -7722,7 +7356,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -7776,15 +7410,10 @@
       <c r="BA62" t="n">
         <v>2</v>
       </c>
-      <c r="BC62" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD62" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE62" t="inlineStr">
+      <c r="BB62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC62" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -7814,7 +7443,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -7829,7 +7458,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -7883,15 +7512,10 @@
       <c r="BA63" t="n">
         <v>2</v>
       </c>
-      <c r="BC63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD63" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE63" t="inlineStr">
+      <c r="BB63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC63" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -7921,7 +7545,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -7936,7 +7560,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -7990,15 +7614,10 @@
       <c r="BA64" t="n">
         <v>2</v>
       </c>
-      <c r="BC64" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD64" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE64" t="inlineStr">
+      <c r="BB64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC64" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -8028,7 +7647,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -8043,7 +7662,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8097,15 +7716,10 @@
       <c r="BA65" t="n">
         <v>2</v>
       </c>
-      <c r="BC65" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD65" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE65" t="inlineStr">
+      <c r="BB65" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC65" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -8135,7 +7749,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -8150,7 +7764,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8204,15 +7818,10 @@
       <c r="BA66" t="n">
         <v>2</v>
       </c>
-      <c r="BC66" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD66" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE66" t="inlineStr">
+      <c r="BB66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC66" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -8242,7 +7851,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -8257,7 +7866,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8311,15 +7920,10 @@
       <c r="BA67" t="n">
         <v>2</v>
       </c>
-      <c r="BC67" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD67" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE67" t="inlineStr">
+      <c r="BB67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC67" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -8349,7 +7953,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -8364,7 +7968,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8418,15 +8022,10 @@
       <c r="BA68" t="n">
         <v>2</v>
       </c>
-      <c r="BC68" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD68" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE68" t="inlineStr">
+      <c r="BB68" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC68" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -8456,7 +8055,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -8471,7 +8070,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8525,15 +8124,10 @@
       <c r="BA69" t="n">
         <v>2</v>
       </c>
-      <c r="BC69" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD69" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE69" t="inlineStr">
+      <c r="BB69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC69" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -8563,7 +8157,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -8578,7 +8172,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -8632,15 +8226,10 @@
       <c r="BA70" t="n">
         <v>2</v>
       </c>
-      <c r="BC70" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD70" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE70" t="inlineStr">
+      <c r="BB70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC70" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -8670,7 +8259,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -8685,7 +8274,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -8739,15 +8328,10 @@
       <c r="BA71" t="n">
         <v>2</v>
       </c>
-      <c r="BC71" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD71" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE71" t="inlineStr">
+      <c r="BB71" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC71" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -8777,7 +8361,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G72" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -8792,7 +8376,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -8846,15 +8430,10 @@
       <c r="BA72" t="n">
         <v>2</v>
       </c>
-      <c r="BC72" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD72" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE72" t="inlineStr">
+      <c r="BB72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC72" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -8884,7 +8463,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G73" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -8899,7 +8478,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -8953,15 +8532,10 @@
       <c r="BA73" t="n">
         <v>2</v>
       </c>
-      <c r="BC73" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD73" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE73" t="inlineStr">
+      <c r="BB73" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC73" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -8991,7 +8565,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G74" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -9006,7 +8580,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -9060,15 +8634,10 @@
       <c r="BA74" t="n">
         <v>2</v>
       </c>
-      <c r="BC74" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD74" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE74" t="inlineStr">
+      <c r="BB74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC74" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -9098,7 +8667,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -9113,7 +8682,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -9167,15 +8736,10 @@
       <c r="BA75" t="n">
         <v>2</v>
       </c>
-      <c r="BC75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD75" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE75" t="inlineStr">
+      <c r="BB75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC75" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -9205,7 +8769,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G76" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -9220,7 +8784,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -9274,15 +8838,10 @@
       <c r="BA76" t="n">
         <v>2</v>
       </c>
-      <c r="BC76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD76" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE76" t="inlineStr">
+      <c r="BB76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC76" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -9312,7 +8871,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -9327,7 +8886,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -9381,15 +8940,10 @@
       <c r="BA77" t="n">
         <v>2</v>
       </c>
-      <c r="BC77" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD77" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE77" t="inlineStr">
+      <c r="BB77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC77" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -9419,7 +8973,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G78" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -9434,7 +8988,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -9488,15 +9042,10 @@
       <c r="BA78" t="n">
         <v>2</v>
       </c>
-      <c r="BC78" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD78" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE78" t="inlineStr">
+      <c r="BB78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC78" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -9526,7 +9075,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -9541,7 +9090,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -9595,15 +9144,10 @@
       <c r="BA79" t="n">
         <v>2</v>
       </c>
-      <c r="BC79" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD79" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE79" t="inlineStr">
+      <c r="BB79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC79" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -9633,7 +9177,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G80" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -9648,7 +9192,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -9702,15 +9246,10 @@
       <c r="BA80" t="n">
         <v>2</v>
       </c>
-      <c r="BC80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD80" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE80" t="inlineStr">
+      <c r="BB80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC80" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -9740,7 +9279,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G81" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -9755,7 +9294,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -9809,15 +9348,10 @@
       <c r="BA81" t="n">
         <v>2</v>
       </c>
-      <c r="BC81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD81" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE81" t="inlineStr">
+      <c r="BB81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC81" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -9847,7 +9381,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G82" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -9862,7 +9396,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -9916,15 +9450,10 @@
       <c r="BA82" t="n">
         <v>2</v>
       </c>
-      <c r="BC82" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD82" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE82" t="inlineStr">
+      <c r="BB82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC82" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -9954,7 +9483,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G83" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -9969,7 +9498,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -10023,15 +9552,10 @@
       <c r="BA83" t="n">
         <v>2</v>
       </c>
-      <c r="BC83" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD83" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE83" t="inlineStr">
+      <c r="BB83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC83" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -10061,7 +9585,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G84" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -10076,7 +9600,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -10130,15 +9654,10 @@
       <c r="BA84" t="n">
         <v>2</v>
       </c>
-      <c r="BC84" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD84" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE84" t="inlineStr">
+      <c r="BB84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC84" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -10168,7 +9687,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G85" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -10183,7 +9702,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -10237,15 +9756,10 @@
       <c r="BA85" t="n">
         <v>2</v>
       </c>
-      <c r="BC85" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD85" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE85" t="inlineStr">
+      <c r="BB85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC85" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -10275,7 +9789,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G86" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -10290,7 +9804,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -10344,15 +9858,10 @@
       <c r="BA86" t="n">
         <v>2</v>
       </c>
-      <c r="BC86" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD86" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE86" t="inlineStr">
+      <c r="BB86" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC86" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -10382,7 +9891,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G87" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -10397,7 +9906,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -10451,15 +9960,10 @@
       <c r="BA87" t="n">
         <v>2</v>
       </c>
-      <c r="BC87" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD87" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE87" t="inlineStr">
+      <c r="BB87" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC87" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -10489,7 +9993,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G88" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -10504,7 +10008,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -10558,15 +10062,10 @@
       <c r="BA88" t="n">
         <v>2</v>
       </c>
-      <c r="BC88" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD88" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE88" t="inlineStr">
+      <c r="BB88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC88" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -10596,7 +10095,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G89" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -10611,7 +10110,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -10665,15 +10164,10 @@
       <c r="BA89" t="n">
         <v>2</v>
       </c>
-      <c r="BC89" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD89" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE89" t="inlineStr">
+      <c r="BB89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC89" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -10703,7 +10197,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G90" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -10718,7 +10212,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -10772,15 +10266,10 @@
       <c r="BA90" t="n">
         <v>2</v>
       </c>
-      <c r="BC90" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD90" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE90" t="inlineStr">
+      <c r="BB90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC90" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -10810,7 +10299,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G91" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -10825,7 +10314,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -10879,15 +10368,10 @@
       <c r="BA91" t="n">
         <v>2</v>
       </c>
-      <c r="BC91" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD91" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE91" t="inlineStr">
+      <c r="BB91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC91" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -10917,7 +10401,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G92" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -10932,7 +10416,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -10986,15 +10470,10 @@
       <c r="BA92" t="n">
         <v>2</v>
       </c>
-      <c r="BC92" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD92" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE92" t="inlineStr">
+      <c r="BB92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC92" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -11024,7 +10503,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G93" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -11039,7 +10518,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -11093,15 +10572,10 @@
       <c r="BA93" t="n">
         <v>2</v>
       </c>
-      <c r="BC93" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD93" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE93" t="inlineStr">
+      <c r="BB93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC93" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -11131,7 +10605,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G94" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -11146,7 +10620,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -11200,15 +10674,10 @@
       <c r="BA94" t="n">
         <v>2</v>
       </c>
-      <c r="BC94" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD94" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE94" t="inlineStr">
+      <c r="BB94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC94" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -11238,7 +10707,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G95" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -11253,7 +10722,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -11307,15 +10776,10 @@
       <c r="BA95" t="n">
         <v>2</v>
       </c>
-      <c r="BC95" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD95" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE95" t="inlineStr">
+      <c r="BB95" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC95" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -11345,7 +10809,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G96" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -11360,7 +10824,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -11414,15 +10878,10 @@
       <c r="BA96" t="n">
         <v>2</v>
       </c>
-      <c r="BC96" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD96" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE96" t="inlineStr">
+      <c r="BB96" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC96" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -11452,7 +10911,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G97" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -11467,7 +10926,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -11521,15 +10980,10 @@
       <c r="BA97" t="n">
         <v>2</v>
       </c>
-      <c r="BC97" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD97" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE97" t="inlineStr">
+      <c r="BB97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC97" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -11559,7 +11013,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G98" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -11574,7 +11028,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -11628,15 +11082,10 @@
       <c r="BA98" t="n">
         <v>2</v>
       </c>
-      <c r="BC98" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD98" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE98" t="inlineStr">
+      <c r="BB98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC98" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -11666,7 +11115,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G99" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -11681,7 +11130,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -11735,15 +11184,10 @@
       <c r="BA99" t="n">
         <v>2</v>
       </c>
-      <c r="BC99" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD99" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE99" t="inlineStr">
+      <c r="BB99" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC99" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -11773,7 +11217,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G100" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -11788,7 +11232,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -11842,15 +11286,10 @@
       <c r="BA100" t="n">
         <v>2</v>
       </c>
-      <c r="BC100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD100" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE100" t="inlineStr">
+      <c r="BB100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC100" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -11880,7 +11319,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G101" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -11895,7 +11334,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -11949,15 +11388,10 @@
       <c r="BA101" t="n">
         <v>2</v>
       </c>
-      <c r="BC101" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD101" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE101" t="inlineStr">
+      <c r="BB101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC101" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -11987,7 +11421,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G102" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -12002,7 +11436,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -12056,15 +11490,10 @@
       <c r="BA102" t="n">
         <v>2</v>
       </c>
-      <c r="BC102" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD102" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE102" t="inlineStr">
+      <c r="BB102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC102" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -12094,7 +11523,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G103" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -12109,7 +11538,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -12163,15 +11592,10 @@
       <c r="BA103" t="n">
         <v>2</v>
       </c>
-      <c r="BC103" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD103" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE103" t="inlineStr">
+      <c r="BB103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC103" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -12201,7 +11625,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G104" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -12216,7 +11640,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -12270,15 +11694,10 @@
       <c r="BA104" t="n">
         <v>2</v>
       </c>
-      <c r="BC104" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD104" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE104" t="inlineStr">
+      <c r="BB104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC104" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -12308,7 +11727,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G105" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -12323,7 +11742,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -12377,15 +11796,10 @@
       <c r="BA105" t="n">
         <v>2</v>
       </c>
-      <c r="BC105" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD105" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE105" t="inlineStr">
+      <c r="BB105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC105" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -12415,7 +11829,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G106" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -12430,7 +11844,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -12484,15 +11898,10 @@
       <c r="BA106" t="n">
         <v>2</v>
       </c>
-      <c r="BC106" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD106" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE106" t="inlineStr">
+      <c r="BB106" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC106" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -12522,7 +11931,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G107" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -12537,7 +11946,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -12591,15 +12000,10 @@
       <c r="BA107" t="n">
         <v>2</v>
       </c>
-      <c r="BC107" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD107" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE107" t="inlineStr">
+      <c r="BB107" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC107" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -12629,7 +12033,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G108" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -12644,7 +12048,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -12698,15 +12102,10 @@
       <c r="BA108" t="n">
         <v>2</v>
       </c>
-      <c r="BC108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD108" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE108" t="inlineStr">
+      <c r="BB108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC108" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -12736,7 +12135,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G109" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -12751,7 +12150,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -12805,15 +12204,10 @@
       <c r="BA109" t="n">
         <v>2</v>
       </c>
-      <c r="BC109" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD109" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE109" t="inlineStr">
+      <c r="BB109" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC109" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -12843,7 +12237,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G110" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -12858,7 +12252,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -12912,15 +12306,10 @@
       <c r="BA110" t="n">
         <v>2</v>
       </c>
-      <c r="BC110" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD110" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE110" t="inlineStr">
+      <c r="BB110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC110" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -12950,7 +12339,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G111" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -12965,7 +12354,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -13019,15 +12408,10 @@
       <c r="BA111" t="n">
         <v>2</v>
       </c>
-      <c r="BC111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD111" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE111" t="inlineStr">
+      <c r="BB111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC111" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -13057,7 +12441,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="G112" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -13072,7 +12456,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -13126,15 +12510,10 @@
       <c r="BA112" t="n">
         <v>2</v>
       </c>
-      <c r="BC112" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD112" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE112" t="inlineStr">
+      <c r="BB112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC112" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -13164,7 +12543,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G113" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -13179,7 +12558,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -13233,15 +12612,10 @@
       <c r="BA113" t="n">
         <v>2</v>
       </c>
-      <c r="BC113" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD113" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE113" t="inlineStr">
+      <c r="BB113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC113" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -13271,7 +12645,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G114" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -13286,7 +12660,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -13340,15 +12714,10 @@
       <c r="BA114" t="n">
         <v>2</v>
       </c>
-      <c r="BC114" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD114" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE114" t="inlineStr">
+      <c r="BB114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC114" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -13378,7 +12747,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G115" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -13393,7 +12762,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -13447,15 +12816,10 @@
       <c r="BA115" t="n">
         <v>2</v>
       </c>
-      <c r="BC115" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD115" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE115" t="inlineStr">
+      <c r="BB115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC115" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -13485,7 +12849,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G116" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -13500,7 +12864,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>China Communications Construction Company</t>
+          <t>China Communications Construction Company International (CCCCI)</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -13554,15 +12918,10 @@
       <c r="BA116" t="n">
         <v>2</v>
       </c>
-      <c r="BC116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD116" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE116" t="inlineStr">
+      <c r="BB116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC116" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -13592,7 +12951,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G117" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -13607,7 +12966,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -13661,15 +13020,10 @@
       <c r="BA117" t="n">
         <v>2</v>
       </c>
-      <c r="BC117" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD117" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE117" t="inlineStr">
+      <c r="BB117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC117" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -13699,7 +13053,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="G118" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -13714,7 +13068,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -13768,15 +13122,10 @@
       <c r="BA118" t="n">
         <v>2</v>
       </c>
-      <c r="BC118" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD118" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE118" t="inlineStr">
+      <c r="BB118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC118" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -13806,7 +13155,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="G119" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -13821,7 +13170,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -13875,15 +13224,10 @@
       <c r="BA119" t="n">
         <v>2</v>
       </c>
-      <c r="BC119" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD119" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE119" t="inlineStr">
+      <c r="BB119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC119" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -13913,7 +13257,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="G120" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -13928,7 +13272,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -13982,15 +13326,10 @@
       <c r="BA120" t="n">
         <v>2</v>
       </c>
-      <c r="BC120" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD120" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE120" t="inlineStr">
+      <c r="BB120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC120" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -14020,7 +13359,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G121" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -14035,7 +13374,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -14089,15 +13428,10 @@
       <c r="BA121" t="n">
         <v>2</v>
       </c>
-      <c r="BC121" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD121" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE121" t="inlineStr">
+      <c r="BB121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC121" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -14127,7 +13461,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G122" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -14142,7 +13476,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -14196,15 +13530,10 @@
       <c r="BA122" t="n">
         <v>2</v>
       </c>
-      <c r="BC122" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD122" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE122" t="inlineStr">
+      <c r="BB122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC122" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -14234,7 +13563,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G123" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -14249,7 +13578,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -14303,15 +13632,10 @@
       <c r="BA123" t="n">
         <v>2</v>
       </c>
-      <c r="BC123" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD123" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE123" t="inlineStr">
+      <c r="BB123" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC123" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -14341,7 +13665,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="G124" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -14356,7 +13680,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -14410,15 +13734,10 @@
       <c r="BA124" t="n">
         <v>2</v>
       </c>
-      <c r="BC124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD124" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE124" t="inlineStr">
+      <c r="BB124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC124" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -14448,7 +13767,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="G125" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -14463,7 +13782,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -14517,15 +13836,10 @@
       <c r="BA125" t="n">
         <v>2</v>
       </c>
-      <c r="BC125" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD125" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE125" t="inlineStr">
+      <c r="BB125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC125" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -14555,7 +13869,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G126" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -14570,7 +13884,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -14624,15 +13938,10 @@
       <c r="BA126" t="n">
         <v>2</v>
       </c>
-      <c r="BC126" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD126" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE126" t="inlineStr">
+      <c r="BB126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC126" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -14662,7 +13971,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G127" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -14677,7 +13986,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -14731,15 +14040,10 @@
       <c r="BA127" t="n">
         <v>2</v>
       </c>
-      <c r="BC127" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD127" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE127" t="inlineStr">
+      <c r="BB127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC127" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -14769,7 +14073,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="G128" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -14784,7 +14088,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -14838,15 +14142,10 @@
       <c r="BA128" t="n">
         <v>2</v>
       </c>
-      <c r="BC128" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD128" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE128" t="inlineStr">
+      <c r="BB128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC128" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -14876,7 +14175,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="G129" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -14891,7 +14190,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -14945,15 +14244,10 @@
       <c r="BA129" t="n">
         <v>2</v>
       </c>
-      <c r="BC129" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD129" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE129" t="inlineStr">
+      <c r="BB129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC129" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
@@ -14983,7 +14277,7 @@
           <t>NIC</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="G130" s="1" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -14998,7 +14292,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -15052,15 +14346,10 @@
       <c r="BA130" t="n">
         <v>2</v>
       </c>
-      <c r="BC130" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD130" t="inlineStr">
-        <is>
-          <t>cancelado</t>
-        </is>
-      </c>
-      <c r="BE130" t="inlineStr">
+      <c r="BB130" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC130" t="inlineStr">
         <is>
           <t>https://www.el19digital.com/articulos/ver/titulo:145846-conozca-los-proyectos-a-ejecutarse-en-nicaragua-con-cooperacion-de-la-republica-popular-china</t>
         </is>
